--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569986348</v>
+        <v>46157.93104270911</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93104270911</v>
+        <v>46157.93176065432</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176065432</v>
+        <v>46157.93401547387</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93401547387</v>
+        <v>46157.93719540412</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93719540412</v>
+        <v>46158.28217695617</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28217695617</v>
+        <v>46158.29683826676</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29683826676</v>
+        <v>46158.2981652688</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981652688</v>
+        <v>46158.33388795247</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388795247</v>
+        <v>46158.36858561367</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858561367</v>
+        <v>46158.37289276154</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
